--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486888_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486888_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1368</v>
+        <v>3.4589</v>
       </c>
       <c r="E2" t="n">
-        <v>1.928</v>
+        <v>2.5169</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2087</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>2.8762</v>
@@ -610,13 +610,13 @@
         <v>1.6427</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.1851</v>
+        <v>-0.8629</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9068000000000001</v>
+        <v>-0.3179</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2783</v>
+        <v>-0.5451</v>
       </c>
       <c r="V2" t="n">
         <v>0.8295</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4383</v>
+        <v>1.7085</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6968</v>
+        <v>2.1152</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2585</v>
+        <v>-0.4067</v>
       </c>
       <c r="G3" t="n">
         <v>2.1654</v>
@@ -688,13 +688,13 @@
         <v>1.4374</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6798999999999999</v>
+        <v>-0.4097</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7091</v>
+        <v>-0.2907</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0293</v>
+        <v>-0.1189</v>
       </c>
       <c r="V3" t="n">
         <v>-0.4579</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7495000000000001</v>
+        <v>0.6045</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0679</v>
+        <v>0.7153</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3183</v>
+        <v>-0.1108</v>
       </c>
       <c r="G4" t="n">
         <v>-4.1149</v>
@@ -766,13 +766,13 @@
         <v>1.4374</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8071</v>
+        <v>-0.9520999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4221</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.2291</v>
+        <v>-1.0216</v>
       </c>
       <c r="V4" t="n">
         <v>4.2341</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>O. THIAM PEDRERA</t>
+          <t>H. FIGUEROA ÁLVAREZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.8384</v>
+        <v>-0.5596</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.2761</v>
+        <v>0.9172</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4377</v>
+        <v>-1.4768</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0391</v>
+        <v>0.5589</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0717</v>
+        <v>-0.101</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1107</v>
+        <v>0.6598000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4093</v>
+        <v>1.4709</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3698</v>
+        <v>-0.5806</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0395</v>
+        <v>2.0515</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3702</v>
+        <v>-0.9121</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4415</v>
+        <v>0.4796</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0713</v>
+        <v>-1.3917</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.616</v>
+        <v>0.2053</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4107</v>
+        <v>1.2321</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2615</v>
+        <v>-0.8659</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6587</v>
+        <v>-0.837</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3973</v>
+        <v>-0.0289</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.4579</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.7679</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. CARREIRA KREPS</t>
+          <t>O. THIAM PEDRERA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.0085</v>
+        <v>-0.7774</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5857</v>
+        <v>-1.0669</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.5942</v>
+        <v>0.2895</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3614</v>
+        <v>0.0391</v>
       </c>
       <c r="H6" t="n">
-        <v>0.07439999999999999</v>
+        <v>-0.0717</v>
       </c>
       <c r="I6" t="n">
-        <v>0.287</v>
+        <v>0.1107</v>
       </c>
       <c r="J6" t="n">
-        <v>2.0735</v>
+        <v>0.4093</v>
       </c>
       <c r="K6" t="n">
-        <v>1.3237</v>
+        <v>0.3698</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7498</v>
+        <v>0.0395</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.7121</v>
+        <v>-0.3702</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.2492</v>
+        <v>-0.4415</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4629</v>
+        <v>0.0713</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.4107</v>
+        <v>-0.616</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R6" t="n">
-        <v>0.616</v>
+        <v>0.4107</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1297</v>
+        <v>-0.2005</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4611</v>
+        <v>-0.4495</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3314</v>
+        <v>0.249</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.8295</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.8295</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>H. FIGUEROA ÁLVAREZ</t>
+          <t>M. CARREIRA KREPS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0125</v>
+        <v>-1.0521</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6421</v>
+        <v>0.6903</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.6547</v>
+        <v>-1.7424</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5589</v>
+        <v>0.3614</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.101</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6598000000000001</v>
+        <v>0.287</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4709</v>
+        <v>2.0735</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.5806</v>
+        <v>1.3237</v>
       </c>
       <c r="L7" t="n">
-        <v>2.0515</v>
+        <v>0.7498</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9121</v>
+        <v>-1.7121</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4796</v>
+        <v>-1.2492</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.3917</v>
+        <v>-0.4629</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2053</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2321</v>
+        <v>0.616</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.3188</v>
+        <v>-0.1733</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.1121</v>
+        <v>-0.3565</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2067</v>
+        <v>0.1832</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.4579</v>
+        <v>-0.8295</v>
       </c>
       <c r="W7" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.7679</v>
+        <v>-0.8295</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. RODRIGUEZ SOLER</t>
+          <t>J. WELLS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0521</v>
+        <v>-1.5842</v>
       </c>
       <c r="E8" t="n">
+        <v>-1.2588</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-0.3254</v>
+      </c>
+      <c r="G8" t="n">
         <v>-0.6915</v>
       </c>
-      <c r="F8" t="n">
-        <v>-0.3606</v>
-      </c>
-      <c r="G8" t="n">
-        <v>-2.4589</v>
-      </c>
       <c r="H8" t="n">
-        <v>-0.6327</v>
+        <v>-1.2199</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.8261</v>
+        <v>0.5284</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.8963</v>
+        <v>-0.2323</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1168</v>
+        <v>-0.363</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.0131</v>
+        <v>0.1307</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5626</v>
+        <v>-0.4592</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7495000000000001</v>
+        <v>-0.8569</v>
       </c>
       <c r="O8" t="n">
-        <v>0.187</v>
+        <v>0.3977</v>
       </c>
       <c r="P8" t="n">
         <v>0.2053</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2053</v>
+        <v>1.2321</v>
       </c>
       <c r="S8" t="n">
-        <v>1.2014</v>
+        <v>-1.4471</v>
       </c>
       <c r="T8" t="n">
-        <v>1.2048</v>
+        <v>-0.5891</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0034</v>
+        <v>-0.858</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.3491</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.5893</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. WELLS</t>
+          <t>G. RODRIGUEZ SOLER</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.7066</v>
+        <v>-1.7547</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.8477</v>
+        <v>-1.4237</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8589</v>
+        <v>-0.331</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.6915</v>
+        <v>-2.4589</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.2199</v>
+        <v>-0.6327</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5284</v>
+        <v>-1.8261</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2323</v>
+        <v>-1.8963</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.363</v>
+        <v>0.1168</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1307</v>
+        <v>-2.0131</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4592</v>
+        <v>-0.5626</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8569</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3977</v>
+        <v>0.187</v>
       </c>
       <c r="P9" t="n">
         <v>0.2053</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2321</v>
+        <v>0.2053</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.5695</v>
+        <v>0.4988</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.178</v>
+        <v>0.4726</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.3915</v>
+        <v>0.0262</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3491</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5893</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8659</v>
+        <v>-3.0092</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1255</v>
+        <v>-0.2688</v>
       </c>
       <c r="F10" t="n">
         <v>-2.7404</v>
@@ -1234,10 +1234,10 @@
         <v>0.616</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7632</v>
+        <v>-0.9066</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4225</v>
+        <v>-0.5658</v>
       </c>
       <c r="U10" t="n">
         <v>-0.3408</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.9461</v>
+        <v>-3.8109</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.4052</v>
+        <v>-4.0328</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4591</v>
+        <v>0.222</v>
       </c>
       <c r="G11" t="n">
         <v>-1.0826</v>
@@ -1312,13 +1312,13 @@
         <v>1.4374</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2371</v>
+        <v>-0.6276</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2167</v>
+        <v>-0.4109</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0204</v>
+        <v>-0.2167</v>
       </c>
       <c r="V11" t="n">
         <v>-0.4579</v>
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.105499999999999</v>
+        <v>-6.7762</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.4255</v>
+        <v>-1.096099999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.680099999999999</v>
+        <v>-5.68</v>
       </c>
       <c r="G12" t="n">
         <v>-1.3531</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1605000000000001</v>
+        <v>0.1604999999999999</v>
       </c>
       <c r="I12" t="n">
         <v>-1.5134</v>
@@ -1369,7 +1369,7 @@
         <v>4.2844</v>
       </c>
       <c r="L12" t="n">
-        <v>2.180400000000001</v>
+        <v>2.1804</v>
       </c>
       <c r="M12" t="n">
         <v>-7.817900000000001</v>
@@ -1390,22 +1390,22 @@
         <v>10.2671</v>
       </c>
       <c r="S12" t="n">
-        <v>-6.276300000000001</v>
+        <v>-5.9469</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.6047</v>
+        <v>-3.2753</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.6714</v>
+        <v>-2.6716</v>
       </c>
       <c r="V12" t="n">
         <v>1.5504</v>
       </c>
       <c r="W12" t="n">
-        <v>7.008000000000001</v>
+        <v>7.007999999999999</v>
       </c>
       <c r="X12" t="n">
-        <v>-5.4577</v>
+        <v>-5.457700000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.127700000000001</v>
+        <v>6.8533</v>
       </c>
       <c r="E13" t="n">
-        <v>7.4081</v>
+        <v>5.9436</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7196</v>
+        <v>0.9096</v>
       </c>
       <c r="G13" t="n">
         <v>2.649</v>
@@ -1468,13 +1468,13 @@
         <v>1.6427</v>
       </c>
       <c r="S13" t="n">
-        <v>2.9859</v>
+        <v>1.7115</v>
       </c>
       <c r="T13" t="n">
-        <v>2.5877</v>
+        <v>1.1233</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3982</v>
+        <v>0.5881999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>1.8768</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.5241</v>
+        <v>3.9914</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2862</v>
+        <v>2.4954</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2379</v>
+        <v>1.496</v>
       </c>
       <c r="G14" t="n">
         <v>3.3399</v>
@@ -1546,13 +1546,13 @@
         <v>1.0267</v>
       </c>
       <c r="S14" t="n">
-        <v>0.11</v>
+        <v>0.5772</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0699</v>
+        <v>0.1393</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1799</v>
+        <v>0.4379</v>
       </c>
       <c r="V14" t="n">
         <v>0.0743</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5644</v>
+        <v>2.7213</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2154</v>
+        <v>1.5292</v>
       </c>
       <c r="F15" t="n">
-        <v>1.349</v>
+        <v>1.1921</v>
       </c>
       <c r="G15" t="n">
         <v>0.2</v>
@@ -1624,13 +1624,13 @@
         <v>1.6427</v>
       </c>
       <c r="S15" t="n">
-        <v>1.019</v>
+        <v>1.1758</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2675</v>
+        <v>0.0463</v>
       </c>
       <c r="U15" t="n">
-        <v>1.2865</v>
+        <v>1.1296</v>
       </c>
       <c r="V15" t="n">
         <v>-0.2973</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. MILADINOVIC</t>
+          <t>M. MUKENDI MUKENDI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9705</v>
+        <v>1.9693</v>
       </c>
       <c r="E16" t="n">
-        <v>3.668</v>
+        <v>0.8327</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.6975</v>
+        <v>1.1367</v>
       </c>
       <c r="G16" t="n">
-        <v>2.1098</v>
+        <v>-0.8476</v>
       </c>
       <c r="H16" t="n">
-        <v>2.5857</v>
+        <v>-1.1031</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4759</v>
+        <v>0.2556</v>
       </c>
       <c r="J16" t="n">
-        <v>3.0801</v>
+        <v>-0.2459</v>
       </c>
       <c r="K16" t="n">
-        <v>3.0011</v>
+        <v>-0.5222</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0789</v>
+        <v>0.2763</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.9702</v>
+        <v>-0.6017</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4154</v>
+        <v>-0.581</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5548</v>
+        <v>-0.0207</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.4107</v>
+        <v>0.616</v>
       </c>
       <c r="Q16" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R16" t="n">
-        <v>0.616</v>
+        <v>1.6427</v>
       </c>
       <c r="S16" t="n">
-        <v>2.5543</v>
+        <v>0.4329</v>
       </c>
       <c r="T16" t="n">
-        <v>2.0725</v>
+        <v>-0.252</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4818</v>
+        <v>0.6849</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.2829</v>
+        <v>1.7679</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.4579</v>
+        <v>2.3573</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.825</v>
+        <v>-0.5893</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. MUKENDI MUKENDI</t>
+          <t>G. MILADINOVIC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2772</v>
+        <v>0.6473</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3096</v>
+        <v>2.4127</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9676</v>
+        <v>-1.7655</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.8476</v>
+        <v>2.1098</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.1031</v>
+        <v>2.5857</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2556</v>
+        <v>-0.4759</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.2459</v>
+        <v>3.0801</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.5222</v>
+        <v>3.0011</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2763</v>
+        <v>0.0789</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6017</v>
+        <v>-0.9702</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.581</v>
+        <v>-0.4154</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0207</v>
+        <v>-0.5548</v>
       </c>
       <c r="P17" t="n">
-        <v>0.616</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6427</v>
+        <v>0.616</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2592</v>
+        <v>1.231</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.775</v>
+        <v>0.8173</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5158</v>
+        <v>0.4137</v>
       </c>
       <c r="V17" t="n">
-        <v>1.7679</v>
+        <v>-2.2829</v>
       </c>
       <c r="W17" t="n">
-        <v>2.3573</v>
+        <v>-0.4579</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5893</v>
+        <v>-1.825</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. CAMPENY LLOVERAS</t>
+          <t>R. TIMONER GIMENEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.203</v>
+        <v>0.5463</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8685</v>
+        <v>0.4936</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6655</v>
+        <v>0.0527</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2293</v>
+        <v>0.7856</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7397</v>
+        <v>-1.359</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5104</v>
+        <v>2.1446</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9344</v>
+        <v>1.6715</v>
       </c>
       <c r="K18" t="n">
-        <v>0.9344</v>
+        <v>-0.7489</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.4204</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.705</v>
+        <v>-0.886</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1947</v>
+        <v>-0.6101</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5104</v>
+        <v>-0.2759</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>0.616</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0263</v>
+        <v>-0.0688</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0659</v>
+        <v>-0.3915</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0395</v>
+        <v>0.3226</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. CASCALES FERNANDEZ</t>
+          <t>P. CAMPENY LLOVERAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5496</v>
+        <v>0.3669</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1185</v>
+        <v>0.9731</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4311</v>
+        <v>-0.6062</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6704</v>
+        <v>0.2293</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.7808</v>
+        <v>0.7397</v>
       </c>
       <c r="I19" t="n">
-        <v>1.1104</v>
+        <v>-0.5104</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0055</v>
+        <v>0.9344</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.3363</v>
+        <v>0.9344</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3418</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6758999999999999</v>
+        <v>-0.705</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4445</v>
+        <v>-0.1947</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2314</v>
+        <v>-0.5104</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2053</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2053</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.08450000000000001</v>
+        <v>0.1375</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.124</v>
+        <v>0.0387</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0395</v>
+        <v>0.0988</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. TIMONER GIMENEZ</t>
+          <t>J. CASCALES FERNANDEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5608</v>
+        <v>-0.2811</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0294</v>
+        <v>0.0907</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5314</v>
+        <v>-0.3718</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7856</v>
+        <v>-0.6704</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.359</v>
+        <v>-1.7808</v>
       </c>
       <c r="I20" t="n">
-        <v>2.1446</v>
+        <v>1.1104</v>
       </c>
       <c r="J20" t="n">
-        <v>1.6715</v>
+        <v>0.0055</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.7489</v>
+        <v>-1.3363</v>
       </c>
       <c r="L20" t="n">
-        <v>2.4204</v>
+        <v>1.3418</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.886</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6101</v>
+        <v>-0.4445</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2759</v>
+        <v>-0.2314</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.4107</v>
+        <v>0.2053</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.616</v>
+        <v>0.2053</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1759</v>
+        <v>0.184</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9145</v>
+        <v>0.0852</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2615</v>
+        <v>0.0988</v>
       </c>
       <c r="V20" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3599</v>
+        <v>-0.788</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.4352</v>
+        <v>-2.1214</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0753</v>
+        <v>1.3334</v>
       </c>
       <c r="G21" t="n">
         <v>-0.7111</v>
@@ -2092,13 +2092,13 @@
         <v>1.6427</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1681</v>
+        <v>0.7399</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0618</v>
+        <v>0.3756</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1063</v>
+        <v>0.3643</v>
       </c>
       <c r="V21" t="n">
         <v>-0.4061</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. MARTÍNEZ-QUINTANILLA JIMÉNEZ</t>
+          <t>J. TAVELLI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.2112</v>
+        <v>-2.2502</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.087</v>
+        <v>-3.5081</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1242</v>
+        <v>1.2578</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.9333</v>
+        <v>-2.8563</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.5256</v>
+        <v>-0.0646</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.4077</v>
+        <v>-2.7917</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.2574</v>
+        <v>-2.5045</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0584</v>
+        <v>0.127</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.3158</v>
+        <v>-2.6315</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.6758999999999999</v>
+        <v>-0.3518</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.584</v>
+        <v>-0.1917</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.092</v>
+        <v>-0.1602</v>
       </c>
       <c r="P22" t="n">
-        <v>0.4107</v>
+        <v>-0.616</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R22" t="n">
-        <v>0.4107</v>
+        <v>1.4374</v>
       </c>
       <c r="S22" t="n">
-        <v>0.7302999999999999</v>
+        <v>1.1478</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1704</v>
+        <v>0.5694</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5599</v>
+        <v>0.5784</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.4189</v>
+        <v>0.0743</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.4805</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.4189</v>
+        <v>-0.4061</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.697</v>
+        <v>-2.4982</v>
       </c>
       <c r="E23" t="n">
         <v>-1.9561</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.7409</v>
+        <v>-0.5421</v>
       </c>
       <c r="G23" t="n">
         <v>-0.9418</v>
@@ -2248,13 +2248,13 @@
         <v>0.4107</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0395</v>
+        <v>0.2383</v>
       </c>
       <c r="T23" t="n">
         <v>0.368</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3285</v>
+        <v>-0.1297</v>
       </c>
       <c r="V23" t="n">
         <v>-1.1786</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. TAVELLI</t>
+          <t>R. MARTÍNEZ-QUINTANILLA JIMÉNEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.1829</v>
+        <v>-2.7778</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.4495</v>
+        <v>-1.5054</v>
       </c>
       <c r="F24" t="n">
-        <v>1.2666</v>
+        <v>-1.2724</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.8563</v>
+        <v>-1.9333</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.0646</v>
+        <v>-0.5256</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.7917</v>
+        <v>-1.4077</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.5045</v>
+        <v>-1.2574</v>
       </c>
       <c r="K24" t="n">
-        <v>0.127</v>
+        <v>0.0584</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.6315</v>
+        <v>-1.3158</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.3518</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.1917</v>
+        <v>-0.584</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.1602</v>
+        <v>-0.092</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.616</v>
+        <v>0.4107</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4374</v>
+        <v>0.4107</v>
       </c>
       <c r="S24" t="n">
-        <v>0.2151</v>
+        <v>0.1637</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3721</v>
+        <v>-0.248</v>
       </c>
       <c r="U24" t="n">
-        <v>0.5872000000000001</v>
+        <v>0.4117</v>
       </c>
       <c r="V24" t="n">
-        <v>0.0743</v>
+        <v>-1.4189</v>
       </c>
       <c r="W24" t="n">
-        <v>0.4805</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.4061</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="25">
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>7.105500000000003</v>
+        <v>8.500499999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>5.680100000000002</v>
+        <v>5.680000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>1.4254</v>
+        <v>2.8203</v>
       </c>
       <c r="G25" t="n">
         <v>1.3531</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.1606</v>
+        <v>-0.1605999999999995</v>
       </c>
       <c r="I25" t="n">
         <v>1.5135</v>
@@ -2386,7 +2386,7 @@
         <v>3.6937</v>
       </c>
       <c r="M25" t="n">
-        <v>-6.464799999999999</v>
+        <v>-6.4648</v>
       </c>
       <c r="N25" t="n">
         <v>-4.2847</v>
@@ -2404,13 +2404,13 @@
         <v>11.2936</v>
       </c>
       <c r="S25" t="n">
-        <v>6.2763</v>
+        <v>7.670800000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>2.671499999999999</v>
+        <v>2.6716</v>
       </c>
       <c r="U25" t="n">
-        <v>3.6046</v>
+        <v>4.9992</v>
       </c>
       <c r="V25" t="n">
         <v>-1.5503</v>
